--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>92057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97399</v>
+        <v>97401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128466179</v>
+        <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517810</v>
+        <v>517760</v>
       </c>
       <c r="R8" t="n">
-        <v>7024664</v>
+        <v>7024714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128466288</v>
+        <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>91358</v>
+        <v>92295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517760</v>
+        <v>517810</v>
       </c>
       <c r="R9" t="n">
-        <v>7024714</v>
+        <v>7024664</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91358</v>
+        <v>91360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>102980</v>
+        <v>102982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97401</v>
+        <v>97494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97401</v>
+        <v>97494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>102982</v>
+        <v>103075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98477</v>
+        <v>98485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97494</v>
+        <v>97500</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97494</v>
+        <v>97500</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103075</v>
+        <v>103086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98485</v>
+        <v>98491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97500</v>
+        <v>97506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97500</v>
+        <v>97506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103086</v>
+        <v>103094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98491</v>
+        <v>98494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97506</v>
+        <v>97508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97506</v>
+        <v>97508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103094</v>
+        <v>103106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98494</v>
+        <v>98497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98497</v>
+        <v>98498</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97508</v>
+        <v>97509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97508</v>
+        <v>97509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98498</v>
+        <v>98525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97509</v>
+        <v>97536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97509</v>
+        <v>97536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98525</v>
+        <v>98531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97536</v>
+        <v>97542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97536</v>
+        <v>97542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98531</v>
+        <v>98538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97542</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97542</v>
+        <v>97549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92434</v>
+        <v>92439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
+        <v>98542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97549</v>
+        <v>97553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98542</v>
+        <v>98549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128466279</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>128466323</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128466305</v>
       </c>
       <c r="B5" t="n">
-        <v>97553</v>
+        <v>97560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>128466207</v>
       </c>
       <c r="B6" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>128466197</v>
       </c>
       <c r="B7" t="n">
-        <v>97553</v>
+        <v>97560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128466288</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>128466179</v>
       </c>
       <c r="B9" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128466215</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466145</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,37 +782,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128466279</v>
+        <v>128466154</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517745</v>
+        <v>517772</v>
       </c>
       <c r="R3" t="n">
-        <v>7024719</v>
+        <v>7024626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera plantor, överblommade</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128466323</v>
+        <v>128466215</v>
       </c>
       <c r="B4" t="n">
-        <v>91515</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517747</v>
+        <v>517723</v>
       </c>
       <c r="R4" t="n">
-        <v>7024782</v>
+        <v>7024674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,38 +990,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128466305</v>
+        <v>128466288</v>
       </c>
       <c r="B5" t="n">
-        <v>97563</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221063</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1023,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517759</v>
+        <v>517760</v>
       </c>
       <c r="R5" t="n">
-        <v>7024748</v>
+        <v>7024714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128466207</v>
+        <v>128466323</v>
       </c>
       <c r="B6" t="n">
-        <v>92213</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517767</v>
+        <v>517747</v>
       </c>
       <c r="R6" t="n">
-        <v>7024686</v>
+        <v>7024782</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128466197</v>
+        <v>128466207</v>
       </c>
       <c r="B7" t="n">
-        <v>97563</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1198,27 +1203,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1226,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517795</v>
+        <v>517767</v>
       </c>
       <c r="R7" t="n">
-        <v>7024677</v>
+        <v>7024686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,32 +1293,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128466288</v>
+        <v>128466179</v>
       </c>
       <c r="B8" t="n">
-        <v>91515</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517760</v>
+        <v>517810</v>
       </c>
       <c r="R8" t="n">
-        <v>7024714</v>
+        <v>7024664</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128466179</v>
+        <v>128466197</v>
       </c>
       <c r="B9" t="n">
-        <v>92451</v>
+        <v>98030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,26 +1405,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517810</v>
+        <v>517795</v>
       </c>
       <c r="R9" t="n">
-        <v>7024664</v>
+        <v>7024677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1496,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128466215</v>
+        <v>128466305</v>
       </c>
       <c r="B10" t="n">
-        <v>91515</v>
+        <v>98030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221063</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1529,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517723</v>
+        <v>517759</v>
       </c>
       <c r="R10" t="n">
-        <v>7024674</v>
+        <v>7024748</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1601,7 @@
         <v>128466165</v>
       </c>
       <c r="B11" t="n">
-        <v>103168</v>
+        <v>103683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54608-2023 artfynd.xlsx
+++ b/artfynd/A 54608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466215</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466323</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466207</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466197</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,8 +1747,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128466165</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>